--- a/diseases/d005/2000-2004.xlsx
+++ b/diseases/d005/2000-2004.xlsx
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42584,7 +42584,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46544,7 +46544,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48920,7 +48920,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51296,7 +51296,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -52484,7 +52484,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -53672,7 +53672,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -56048,7 +56048,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -57236,7 +57236,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -58424,7 +58424,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">

--- a/diseases/d005/2000-2004.xlsx
+++ b/diseases/d005/2000-2004.xlsx
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42584,7 +42584,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46544,7 +46544,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48920,7 +48920,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51296,7 +51296,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -52484,7 +52484,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -53672,7 +53672,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -56048,7 +56048,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -57236,7 +57236,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -58424,7 +58424,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">

--- a/diseases/d005/2000-2004.xlsx
+++ b/diseases/d005/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.3555176336746302</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>4</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>3</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>7</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.3508125696143693</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>7</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>2</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>8</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.1772398744521349</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>5</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>4</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>2</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>3</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>8</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>3</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>2</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>2</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>4</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>3</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.3452979057682015</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>24</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.1058942294461893</v>
       </c>
@@ -31902,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>3</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>4</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>14</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.06177163384361041</v>
       </c>
@@ -33090,7 +32844,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>9</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>28</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.1235432676872208</v>
       </c>
@@ -34278,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>3</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>3</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>33</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.1456045654885103</v>
       </c>
@@ -35466,7 +35202,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>3</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>10</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.04412259560257887</v>
       </c>
@@ -36654,7 +36381,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>3</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>2</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -37593,9 +37314,6 @@
       <c r="O188" t="n">
         <v>19</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.08383293164489986</v>
       </c>
@@ -37842,7 +37560,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37989,9 +37707,6 @@
       <c r="O190" t="n">
         <v>2</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -38385,9 +38100,6 @@
       <c r="O192" t="n">
         <v>8</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -38781,9 +38493,6 @@
       <c r="O194" t="n">
         <v>22</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.09706971032567351</v>
       </c>
@@ -39030,7 +38739,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39177,9 +38886,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -39573,9 +39279,6 @@
       <c r="O198" t="n">
         <v>6</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -39969,9 +39672,6 @@
       <c r="O200" t="n">
         <v>30</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1323677868077366</v>
       </c>
@@ -40218,7 +39918,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40365,9 +40065,6 @@
       <c r="O202" t="n">
         <v>4</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -40761,9 +40458,6 @@
       <c r="O204" t="n">
         <v>2</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -41157,9 +40851,6 @@
       <c r="O206" t="n">
         <v>27</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.1191310081269629</v>
       </c>
@@ -41406,7 +41097,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41553,9 +41244,6 @@
       <c r="O208" t="n">
         <v>2</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -41949,9 +41637,6 @@
       <c r="O210" t="n">
         <v>2</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -42345,9 +42030,6 @@
       <c r="O212" t="n">
         <v>15</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.06618389340386829</v>
       </c>
@@ -42594,7 +42276,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42741,9 +42423,6 @@
       <c r="O214" t="n">
         <v>2</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -43137,9 +42816,6 @@
       <c r="O216" t="n">
         <v>5</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -43533,9 +43209,6 @@
       <c r="O218" t="n">
         <v>25</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.1103064890064472</v>
       </c>
@@ -43782,7 +43455,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43929,9 +43602,6 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -44325,9 +43995,6 @@
       <c r="O222" t="n">
         <v>8</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -44721,9 +44388,6 @@
       <c r="O224" t="n">
         <v>27</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.1191310081269629</v>
       </c>
@@ -44970,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45117,9 +44781,6 @@
       <c r="O226" t="n">
         <v>2</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -45513,9 +45174,6 @@
       <c r="O228" t="n">
         <v>3</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>1.02680473767706</v>
       </c>
@@ -45909,9 +45567,6 @@
       <c r="O230" t="n">
         <v>3</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -46305,9 +45960,6 @@
       <c r="O232" t="n">
         <v>28</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.1231016462163324</v>
       </c>
@@ -46554,7 +46206,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46701,9 +46353,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -47097,9 +46746,6 @@
       <c r="O236" t="n">
         <v>4</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -47493,9 +47139,6 @@
       <c r="O238" t="n">
         <v>21</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.0923262346622493</v>
       </c>
@@ -47742,7 +47385,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47889,9 +47532,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -48285,9 +47925,6 @@
       <c r="O242" t="n">
         <v>4</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -48681,9 +48318,6 @@
       <c r="O244" t="n">
         <v>17</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.07474028520277325</v>
       </c>
@@ -48930,7 +48564,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -49077,9 +48711,6 @@
       <c r="O246" t="n">
         <v>3</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -49473,9 +49104,6 @@
       <c r="O248" t="n">
         <v>3</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -49869,9 +49497,6 @@
       <c r="O250" t="n">
         <v>40</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.1758594945947606</v>
       </c>
@@ -50118,7 +49743,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -50265,9 +49890,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -50661,9 +50283,6 @@
       <c r="O254" t="n">
         <v>3</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -51057,9 +50676,6 @@
       <c r="O256" t="n">
         <v>22</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.09672272202711832</v>
       </c>
@@ -51306,7 +50922,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51453,9 +51069,6 @@
       <c r="O258" t="n">
         <v>1</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -51849,9 +51462,6 @@
       <c r="O260" t="n">
         <v>4</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -52245,9 +51855,6 @@
       <c r="O262" t="n">
         <v>20</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.0879297472973803</v>
       </c>
@@ -52494,7 +52101,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52641,9 +52248,6 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -53037,9 +52641,6 @@
       <c r="O266" t="n">
         <v>3</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -53433,9 +53034,6 @@
       <c r="O268" t="n">
         <v>18</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.07913677256764227</v>
       </c>
@@ -53682,7 +53280,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -53829,9 +53427,6 @@
       <c r="O270" t="n">
         <v>4</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -54225,9 +53820,6 @@
       <c r="O272" t="n">
         <v>2</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -54621,9 +54213,6 @@
       <c r="O274" t="n">
         <v>34</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.1494805704055465</v>
       </c>
@@ -54870,7 +54459,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -55017,9 +54606,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -55413,9 +54999,6 @@
       <c r="O278" t="n">
         <v>4</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -55809,9 +55392,6 @@
       <c r="O280" t="n">
         <v>19</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.08353325993251128</v>
       </c>
@@ -56058,7 +55638,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -56205,9 +55785,6 @@
       <c r="O282" t="n">
         <v>3</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -56601,9 +56178,6 @@
       <c r="O284" t="n">
         <v>3</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -56997,9 +56571,6 @@
       <c r="O286" t="n">
         <v>24</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.1055156967568564</v>
       </c>
@@ -57246,7 +56817,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -57393,9 +56964,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -57789,9 +57357,6 @@
       <c r="O290" t="n">
         <v>2</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -58185,9 +57750,6 @@
       <c r="O292" t="n">
         <v>18</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.07913677256764227</v>
       </c>
@@ -58434,7 +57996,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58581,9 +58143,6 @@
       <c r="O294" t="n">
         <v>1</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -58977,9 +58536,6 @@
       <c r="O296" t="n">
         <v>1</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -59373,9 +58929,6 @@
       <c r="O298" t="n">
         <v>31</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.1362911083109395</v>
       </c>
@@ -59622,7 +59175,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">

--- a/diseases/d005/2000-2004.xlsx
+++ b/diseases/d005/2000-2004.xlsx
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37550,7 +37550,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39908,7 +39908,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44624,7 +44624,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48554,7 +48554,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -49733,7 +49733,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50912,7 +50912,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -52091,7 +52091,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -53270,7 +53270,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -54449,7 +54449,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55628,7 +55628,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56807,7 +56807,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -57986,7 +57986,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -59165,7 +59165,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
